--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0003T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.88405828386188</v>
+        <v>7.293659471127555</v>
       </c>
       <c r="D2" t="n">
-        <v>46.88508828780567</v>
+        <v>7.618826846768421</v>
       </c>
       <c r="E2" t="n">
-        <v>7.375139554295503</v>
+        <v>1.198460177573019</v>
       </c>
       <c r="F2" t="n">
-        <v>6.819918824879895</v>
+        <v>1.108236809042983</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.84857153760827</v>
+        <v>7.612892874861345</v>
       </c>
       <c r="D3" t="n">
-        <v>41.08800218568812</v>
+        <v>6.676800355174319</v>
       </c>
       <c r="E3" t="n">
-        <v>7.375139554295503</v>
+        <v>1.198460177573019</v>
       </c>
       <c r="F3" t="n">
-        <v>6.819918824879895</v>
+        <v>1.108236809042983</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.31406133574169</v>
+        <v>4.926034967058025</v>
       </c>
       <c r="D4" t="n">
-        <v>30.41834115351403</v>
+        <v>4.94298043744603</v>
       </c>
       <c r="E4" t="n">
-        <v>7.375139554295503</v>
+        <v>1.198460177573019</v>
       </c>
       <c r="F4" t="n">
-        <v>6.819918824879895</v>
+        <v>1.108236809042983</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
